--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>66.7</v>
+        <v>65.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1930,14 +1930,14 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>51.9</v>
+        <v>37.3</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>63.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>54.5</v>
+        <v>42.9</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2102,44 +2102,48 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-U</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E27" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-D</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
       <c r="L27" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>60</v>
+      </c>
       <c r="O27" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2211,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2220,10 +2224,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>88.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2231,14 +2235,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>53.8</v>
+        <v>59.8</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2247,10 +2251,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>85.7</v>
+        <v>66.7</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2258,10 +2262,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>57.1</v>
+        <v>59.3</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -2272,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2281,10 +2285,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>42.6</v>
+        <v>50.9</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2292,37 +2296,37 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>44.1</v>
+        <v>43</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>48.4</v>
+        <v>53.3</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>45.2</v>
+        <v>40</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
@@ -2760,7 +2764,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2769,25 +2773,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>64.8</v>
+        <v>63.8</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>43.2</v>
+        <v>44.7</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2796,21 +2800,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>62.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39">
@@ -2943,7 +2947,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2952,10 +2956,10 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>55.6</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2963,14 +2967,14 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2982,7 +2986,7 @@
         <v>75</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2994,10 @@
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -3370,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3379,25 +3383,25 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>61.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>44.9</v>
+        <v>43.5</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3406,21 +3410,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>60.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49">
@@ -3431,7 +3435,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3440,10 +3444,10 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>57.1</v>
+        <v>51</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3451,26 +3455,26 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>36.4</v>
+        <v>45.1</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -3478,10 +3482,10 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>39.3</v>
+        <v>46.6</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50">
@@ -3919,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3928,25 +3932,25 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>36.8</v>
+        <v>37.5</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-D</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3955,21 +3959,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>70</v>
+        <v>64.3</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
@@ -4041,7 +4045,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4050,10 +4054,10 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>65.5</v>
+        <v>72.5</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -4061,14 +4065,14 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>41.4</v>
+        <v>42.5</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4077,21 +4081,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>63.6</v>
+        <v>80</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>63.6</v>
+        <v>40</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
@@ -4224,7 +4228,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4233,10 +4237,10 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>77.8</v>
+        <v>63.6</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -4244,14 +4248,14 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>44.4</v>
+        <v>41.8</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4260,10 +4264,10 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>73.7</v>
+        <v>79.2</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -4271,10 +4275,10 @@
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>47.4</v>
+        <v>41.7</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
@@ -4285,7 +4289,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4294,10 +4298,10 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>93.8</v>
+        <v>62.5</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -4308,11 +4312,11 @@
         <v>43.8</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4321,21 +4325,21 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
@@ -4529,53 +4533,57 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>100</v>
+        <v>47.4</v>
       </c>
       <c r="E67" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>N-U-D-D</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L67" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="G67" s="3" t="n">
+      <c r="N67" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H67" s="4" t="n">
+      <c r="O67" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>N-U-D-N</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr"/>
-      <c r="L67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N67" s="3" t="inlineStr"/>
-      <c r="O67" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4647,57 +4655,57 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>60.4</v>
+        <v>60.9</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>47.2</v>
+        <v>50</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>52.4</v>
+        <v>63.2</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>42.9</v>
+        <v>52.6</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
@@ -4769,7 +4777,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4778,25 +4786,25 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>63.1</v>
+        <v>53.2</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>40.8</v>
+        <v>43</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4805,18 +4813,18 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>60.7</v>
+        <v>55.7</v>
       </c>
       <c r="L71" s="4" t="n">
         <v>61</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>39.3</v>
+        <v>47.5</v>
       </c>
       <c r="O71" s="4" t="n">
         <v>61</v>
@@ -4830,7 +4838,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4839,10 +4847,10 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>45.9</v>
+        <v>52.7</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4850,14 +4858,14 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>49.4</v>
+        <v>42.9</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4866,10 +4874,10 @@
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>44.7</v>
+        <v>66.7</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -4877,10 +4885,10 @@
         </is>
       </c>
       <c r="N72" s="3" t="n">
-        <v>55.3</v>
+        <v>50</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73">
@@ -5318,7 +5326,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5327,10 +5335,10 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>47.3</v>
+        <v>61.9</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -5338,37 +5346,37 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>35.1</v>
+        <v>40.5</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>42.4</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>42.4</v>
+        <v>35.3</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
@@ -6477,7 +6485,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6486,10 +6494,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>61</v>
+        <v>56.9</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6497,14 +6505,14 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>40.3</v>
+        <v>38.9</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6513,10 +6521,10 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -6524,10 +6532,10 @@
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>52</v>
+        <v>41.7</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100">
@@ -6721,7 +6729,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6730,25 +6738,25 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>53.5</v>
+        <v>61.7</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>43.4</v>
+        <v>35.8</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6757,10 +6765,10 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>48.5</v>
+        <v>58.3</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6776,10 @@
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104">
@@ -8576,7 +8584,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8585,48 +8593,48 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>57.1</v>
+        <v>72.7</v>
       </c>
       <c r="G24" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N24" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J24" s="4" t="n">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Q24" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q24" s="4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -8789,34 +8797,34 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="J27" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -8927,7 +8935,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8936,48 +8944,48 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J29" s="4" t="n">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Q29" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-N</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q29" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -8998,19 +9006,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>33.3</v>
+        <v>48.3</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -9018,37 +9026,37 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>77.8</v>
+        <v>41.4</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="N30" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>60</v>
-      </c>
       <c r="Q30" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -9566,7 +9574,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9575,25 +9583,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>63.2</v>
+        <v>76.5</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>52.6</v>
+        <v>58.8</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -9605,18 +9613,18 @@
         <v>75</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
@@ -9779,19 +9787,19 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -9799,37 +9807,33 @@
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -10272,7 +10276,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10281,10 +10285,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>58.8</v>
+        <v>68.2</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -10292,14 +10296,14 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>41.2</v>
+        <v>45.5</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10308,21 +10312,21 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>52.4</v>
+        <v>66.7</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>38.1</v>
+        <v>66.7</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -10343,57 +10347,57 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>55</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>46.2</v>
+        <v>60</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -10907,7 +10911,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10916,10 +10920,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>63.6</v>
+        <v>90</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -10927,14 +10931,14 @@
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>54.5</v>
+        <v>40</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-D</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -10943,21 +10947,21 @@
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -11049,7 +11053,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11058,48 +11062,44 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>73.3</v>
+        <v>87.5</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>46.7</v>
+        <v>37.5</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr"/>
       <c r="Q59" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11271,25 +11271,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>83.3</v>
+        <v>73.7</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>50</v>
+        <v>36.8</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -11298,10 +11298,10 @@
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>75</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -11309,10 +11309,10 @@
         </is>
       </c>
       <c r="P62" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -11342,25 +11342,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -11369,10 +11369,10 @@
         </is>
       </c>
       <c r="M63" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -11380,10 +11380,10 @@
         </is>
       </c>
       <c r="P63" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -11617,30 +11617,34 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="G67" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>60</v>
+      </c>
       <c r="J67" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -11751,7 +11755,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -11760,37 +11764,37 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I69" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M69" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -11801,7 +11805,7 @@
         <v>100</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -11893,7 +11897,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -11902,25 +11906,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>64.3</v>
+        <v>75.8</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I71" s="3" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -11929,21 +11933,21 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>61.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P71" s="3" t="n">
-        <v>38.5</v>
+        <v>54.5</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
@@ -11964,46 +11968,46 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="G72" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>70</v>
-      </c>
       <c r="J72" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M72" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -12011,10 +12015,10 @@
         </is>
       </c>
       <c r="P72" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -12532,7 +12536,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -12541,48 +12545,48 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -13881,7 +13885,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13890,48 +13894,48 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -14165,7 +14169,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -14174,10 +14178,10 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>55.6</v>
+        <v>53.8</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -14185,37 +14189,37 @@
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>48.1</v>
+        <v>53.8</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M103" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="N103" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>46.2</v>
+        <v>100</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1614,25 +1614,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>49.5</v>
+        <v>53.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>47.3</v>
+        <v>46.3</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1641,21 +1641,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>64.3</v>
+        <v>57.1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,25 +1675,25 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>70.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>38.9</v>
+        <v>41</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>61.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>41.7</v>
+        <v>40.6</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -3740,57 +3740,57 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>44.4</v>
+        <v>58.6</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>55.6</v>
+        <v>41.4</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4908,25 +4908,25 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>72.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>42.5</v>
+        <v>46.8</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4935,21 +4935,21 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>72.7</v>
+        <v>71.8</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>63.6</v>
+        <v>51.3</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8242,10 +8242,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>58.3</v>
+        <v>62.5</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -8253,33 +8253,37 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -8300,7 +8304,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8309,25 +8313,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>87.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>43.8</v>
+        <v>46.2</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8336,21 +8340,21 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>75</v>
+        <v>73.3</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -10702,7 +10706,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10711,25 +10715,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -12039,7 +12043,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12048,25 +12052,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>85.7</v>
+        <v>47.4</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -12075,21 +12079,21 @@
         </is>
       </c>
       <c r="M73" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>53.6</v>
+        <v>58.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -649,14 +649,14 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>44.4</v>
+        <v>39.4</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>47.5</v>
+        <v>58.5</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>42.4</v>
+        <v>46.2</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -760,25 +760,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>56.3</v>
+        <v>75</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>46.5</v>
+        <v>40.4</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>40.5</v>
+        <v>52.2</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>72.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>45.5</v>
+        <v>55.6</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -954,14 +954,14 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>81</v>
+        <v>77.8</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1126,25 +1126,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>61.8</v>
+        <v>59.2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>51.2</v>
+        <v>44.9</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>61.9</v>
+        <v>64.7</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>54.8</v>
+        <v>47.1</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>64.3</v>
+        <v>61.3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>42.9</v>
+        <v>54.8</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -1605,57 +1605,57 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>53.3</v>
+        <v>42.9</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>63.3</v>
+        <v>46.4</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1980,25 +1980,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>37.8</v>
+        <v>42.5</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>87.5</v>
+        <v>70.3</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>62.5</v>
+        <v>45.9</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>108</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>78</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="L31" s="4" t="n">
         <v>40</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2529,25 +2529,25 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>65.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>50</v>
+        <v>40.6</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2556,21 +2556,21 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>65.2</v>
+        <v>63.6</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>56.5</v>
+        <v>48.5</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2590,48 +2590,48 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-U</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="L35" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="H35" s="4" t="n">
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="O35" s="4" t="n">
         <v>25</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2651,25 +2651,25 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>48.6</v>
+        <v>60.7</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>48.6</v>
+        <v>53.6</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>50</v>
+        <v>64.7</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>50</v>
+        <v>64.7</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3139,25 +3139,25 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>89.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>52.6</v>
+        <v>44.9</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>100</v>
+        <v>59.1</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>42.9</v>
+        <v>40.9</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3394,14 +3394,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>34.6</v>
+        <v>43.8</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,21 +3410,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>46.4</v>
+        <v>50</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>56.9</v>
+        <v>54.9</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>51</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,48 +3688,48 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-D</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E53" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-N</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="L53" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,25 +3749,25 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>58.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>41.4</v>
+        <v>44.3</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>75</v>
+        <v>41.7</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>65.8</v>
+        <v>52.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3821,14 +3821,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3837,21 +3837,21 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>63.6</v>
+        <v>57.1</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,25 +3993,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>70</v>
+        <v>54.1</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4023,18 +4023,18 @@
         <v>75</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4359,25 +4359,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>49</v>
+        <v>42.6</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>43.4</v>
+        <v>47</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>47.7</v>
+        <v>45.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>44.2</v>
+        <v>40.6</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4725,25 +4725,25 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>57.7</v>
+        <v>54.8</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>42.3</v>
+        <v>43.7</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>65.2</v>
+        <v>59.6</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>52.2</v>
+        <v>44.2</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4908,48 +4908,48 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>60.5</v>
+        <v>66.7</v>
       </c>
       <c r="E73" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="L73" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="H73" s="4" t="n">
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="O73" s="4" t="n">
         <v>38</v>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N73" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="O73" s="4" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>51.6</v>
+        <v>52.1</v>
       </c>
       <c r="E78" s="4" t="n">
         <v>192</v>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5274,25 +5274,25 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>72.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5301,21 +5301,21 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>40</v>
+        <v>46.7</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>52.4</v>
+        <v>53.3</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -5346,14 +5346,14 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>57.1</v>
+        <v>52.9</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>35.7</v>
+        <v>35.3</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5457,25 +5457,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>72.7</v>
+        <v>68.3</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>45.5</v>
+        <v>43.9</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>83.3</v>
+        <v>70</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>57.6</v>
+        <v>51.5</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5895,14 +5895,14 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>39.4</v>
+        <v>47</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>70</v>
+        <v>48.1</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>40</v>
+        <v>51.9</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6250,25 +6250,25 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>68.2</v>
+        <v>79.5</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>67.7</v>
+        <v>83.3</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>67.7</v>
+        <v>58.3</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6555,25 +6555,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>60.1</v>
+        <v>53.6</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>39.2</v>
+        <v>46.4</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>54.5</v>
+        <v>51.7</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>42.4</v>
+        <v>51.7</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6677,25 +6677,25 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>76.5</v>
+        <v>70.7</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>42.6</v>
+        <v>40.2</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>68.2</v>
+        <v>69</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>40.9</v>
+        <v>37.9</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>68</v>
+        <v>55.6</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7117,37 +7117,37 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>52</v>
+        <v>48.9</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>69.2</v>
+        <v>37.5</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>38.5</v>
+        <v>56.2</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>58.3</v>
+        <v>90</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7259,14 +7259,14 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7275,21 +7275,21 @@
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7319,48 +7319,48 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>63.6</v>
+        <v>54.5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -7448,57 +7448,57 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7661,19 +7661,19 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7681,14 +7681,14 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7697,21 +7697,21 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7812,44 +7812,48 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="N13" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q13" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -8225,7 +8229,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8234,48 +8238,48 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -8647,7 +8651,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8656,10 +8660,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>91.7</v>
+        <v>70</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -8667,14 +8671,14 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -8683,21 +8687,21 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9286,7 +9290,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9295,10 +9299,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -9306,37 +9310,37 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>41.2</v>
+        <v>61.5</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M34" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="Q34" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -9357,7 +9361,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9369,7 +9373,7 @@
         <v>75</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -9380,34 +9384,34 @@
         <v>75</v>
       </c>
       <c r="J35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-U</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N35" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -9428,7 +9432,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9437,41 +9441,41 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
@@ -9992,7 +9996,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10001,48 +10005,48 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G44" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-D</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="N44" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="n">
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="J44" s="4" t="n">
+      <c r="Q44" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q44" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -10276,7 +10280,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10285,48 +10289,48 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>70</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G48" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-D</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="N48" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J48" s="4" t="n">
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q48" s="4" t="n">
         <v>10</v>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>U-D-N-N</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="Q48" s="4" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -10631,49 +10635,57 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="G53" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="J53" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P53" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -10694,7 +10706,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10703,41 +10715,41 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N54" s="4" t="n">
         <v>2</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P54" s="3" t="n">
@@ -10765,7 +10777,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10774,10 +10786,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -10785,14 +10797,14 @@
         </is>
       </c>
       <c r="I55" s="3" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="J55" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="J55" s="4" t="n">
-        <v>15</v>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -10801,21 +10813,21 @@
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>100</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>66.7</v>
+        <v>69.2</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -10978,19 +10990,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>50</v>
+        <v>76.5</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -10998,33 +11010,37 @@
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>50</v>
+        <v>64.7</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N58" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q58" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -11400,7 +11416,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11409,25 +11425,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>56</v>
+        <v>48.6</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>40</v>
+        <v>45.9</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -11436,10 +11452,10 @@
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>44.4</v>
+        <v>54.5</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -11447,10 +11463,10 @@
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -11818,7 +11834,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11827,10 +11843,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>54.5</v>
+        <v>60</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -11838,14 +11854,14 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>63.6</v>
+        <v>46.7</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -11857,7 +11873,7 @@
         <v>66.7</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -11865,10 +11881,10 @@
         </is>
       </c>
       <c r="P70" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -12031,7 +12047,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12040,44 +12056,48 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>80</v>
+        <v>57.1</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>57.1</v>
+      </c>
       <c r="N73" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
       <c r="Q73" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -12453,7 +12473,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12462,48 +12482,48 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I79" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-D</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="N79" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J79" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>33.3</v>
-      </c>
       <c r="Q79" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80">
@@ -12524,7 +12544,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -12533,48 +12553,48 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>75</v>
+        <v>58.8</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>N-U-N-D</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J80" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>N-U-N-N</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M80" s="3" t="n">
-        <v>80</v>
-      </c>
       <c r="N80" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -12666,7 +12686,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12675,44 +12695,48 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>100</v>
+        <v>69.2</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>75</v>
+        <v>46.2</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="N82" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P82" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>37.5</v>
+      </c>
       <c r="Q82" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -13159,43 +13183,43 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>57.1</v>
+        <v>33.3</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="N89" s="4" t="n">
         <v>3</v>
@@ -13585,7 +13609,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13594,25 +13618,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>53.8</v>
+        <v>57.1</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13621,21 +13645,21 @@
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -13940,7 +13964,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -13949,10 +13973,10 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>79.2</v>
+        <v>52</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -13960,14 +13984,14 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>45.8</v>
+        <v>48</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -13976,21 +14000,21 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>75</v>
+        <v>61.5</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101">
@@ -14082,7 +14106,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14091,7 +14115,7 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="G102" s="4" t="n">
         <v>15</v>
@@ -14102,14 +14126,14 @@
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>53.3</v>
+        <v>46.7</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14118,21 +14142,21 @@
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>42.9</v>
+        <v>75</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -751,7 +751,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -760,25 +760,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>75</v>
+        <v>75.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>40.4</v>
+        <v>35.1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>75</v>
+        <v>76.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>33.3</v>
+        <v>47.1</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -954,14 +954,14 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>77.8</v>
+        <v>81</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,25 +1004,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>48.7</v>
+        <v>40.7</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>84.8</v>
+        <v>77.8</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>39.4</v>
+        <v>44.4</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>59.2</v>
+        <v>65.2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1137,14 +1137,14 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>44.9</v>
+        <v>47.1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>64.7</v>
+        <v>61.9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>47.1</v>
+        <v>42.9</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>17</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
@@ -1788,57 +1788,57 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>47.9</v>
+        <v>55.6</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>43.7</v>
+        <v>50</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>45.7</v>
+        <v>70</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>45.7</v>
+        <v>50</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2235,14 +2235,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>60.2</v>
+        <v>53.8</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>75</v>
+        <v>86.7</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>60.9</v>
+        <v>46.7</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2590,25 +2590,25 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>50.9</v>
+        <v>44.2</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2617,21 +2617,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>64</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>56</v>
+        <v>41.7</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>60.7</v>
+        <v>63.1</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2662,14 +2662,14 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>53.6</v>
+        <v>43.1</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>64.7</v>
+        <v>47.4</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>64.7</v>
+        <v>47.4</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2956,25 +2956,25 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3078,25 +3078,25 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>75</v>
+        <v>88.2</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>44.4</v>
+        <v>47.1</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>76.5</v>
+        <v>100</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>41.2</v>
+        <v>50</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -4533,19 +4533,19 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -4553,26 +4553,26 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>66.7</v>
+        <v>43.8</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4664,25 +4664,25 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>53.2</v>
+        <v>50</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>47.8</v>
+        <v>52.4</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>47.8</v>
+        <v>52.4</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5213,25 +5213,25 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>52.1</v>
+        <v>56.1</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>50.5</v>
+        <v>43.9</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="L78" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N78" s="3" t="n">
-        <v>56.2</v>
-      </c>
       <c r="O78" s="4" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>58.1</v>
+        <v>69</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5773,14 +5773,14 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>45.9</v>
+        <v>36.8</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5789,21 +5789,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>42.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>44.2</v>
+        <v>46.4</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6128,25 +6128,25 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>34.8</v>
+        <v>42.9</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>89.5</v>
+        <v>79.2</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>52.6</v>
+        <v>45.8</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7248,25 +7248,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>90</v>
+        <v>61.1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>60</v>
+        <v>44.4</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>3</v>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q5" s="4" t="n">
         <v>3</v>
@@ -7448,57 +7448,57 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7531,22 +7531,22 @@
         <v>66.7</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>59.3</v>
+        <v>46.7</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -7661,57 +7661,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="Q11" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -8442,34 +8442,34 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>56.2</v>
+        <v>50</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -8478,21 +8478,21 @@
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8944,25 +8944,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>73.7</v>
+        <v>87.5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>63.2</v>
+        <v>62.5</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -8971,21 +8971,21 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>8</v>
@@ -9381,14 +9381,14 @@
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -9408,10 +9408,10 @@
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>66.7</v>
+        <v>61.1</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -9452,37 +9452,37 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J36" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="N36" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9799,41 +9799,45 @@
         <v>100</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>D-N-N-D</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>D-N-N-N</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q41" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -9925,7 +9929,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9934,25 +9938,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -9964,18 +9968,18 @@
         <v>100</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -11629,49 +11633,57 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="G67" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="J67" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="N67" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q67" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -11763,7 +11775,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -11772,10 +11784,10 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>62.5</v>
+        <v>44.4</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -11783,34 +11795,34 @@
         </is>
       </c>
       <c r="I69" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M69" s="3" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P69" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q69" s="4" t="n">
         <v>3</v>
@@ -12402,7 +12414,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12411,25 +12423,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>63.2</v>
+        <v>48</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>55.3</v>
+        <v>46</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -12438,21 +12450,21 @@
         </is>
       </c>
       <c r="M78" s="3" t="n">
-        <v>55.6</v>
+        <v>54.2</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>55.6</v>
+        <v>54.2</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
@@ -13041,7 +13053,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13050,10 +13062,10 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>60.7</v>
+        <v>72.2</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -13061,37 +13073,37 @@
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>35.7</v>
+        <v>44.4</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -13467,7 +13479,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -13476,48 +13488,48 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J93" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>D-N-N-D</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N93" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P93" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G93" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J93" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>D-N-N-N</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M93" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N93" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P93" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q93" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -954,14 +954,14 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>81</v>
+        <v>77.8</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>88.5</v>
+        <v>62.2</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2235,14 +2235,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>53.8</v>
+        <v>57.8</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>86.7</v>
+        <v>57.1</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46.7</v>
+        <v>57.1</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3078,25 +3078,25 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>88.2</v>
+        <v>69.2</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3105,14 +3105,14 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L43" s="4" t="n">
         <v>8</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>52.9</v>
+        <v>49.7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3211,14 +3211,14 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>34.1</v>
+        <v>45.1</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>53.1</v>
+        <v>53.8</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>34.7</v>
+        <v>45</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6250,25 +6250,25 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>79.5</v>
+        <v>60</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>46.2</v>
+        <v>49.6</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>83.3</v>
+        <v>56.8</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>47.9</v>
+        <v>56.3</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6505,14 +6505,14 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>37</v>
+        <v>56.3</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6524,18 +6524,18 @@
         <v>50</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>54.2</v>
+        <v>57.1</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100">
@@ -7448,57 +7448,57 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8944,25 +8944,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>87.5</v>
+        <v>81.8</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>62.5</v>
+        <v>63.6</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -8971,21 +8971,21 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9941,22 +9941,22 @@
         <v>100</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10080,25 +10080,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>41.2</v>
+        <v>47.9</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -10107,21 +10107,21 @@
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>54.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>36.4</v>
+        <v>57.9</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13630,25 +13630,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>57.1</v>
+        <v>46.4</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13657,21 +13657,21 @@
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>100</v>
+        <v>77.8</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
@@ -13905,46 +13905,46 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>43.5</v>
+        <v>62.5</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>39.1</v>
+        <v>41.7</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>42.9</v>
+        <v>77.8</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -13952,10 +13952,10 @@
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>58.1</v>
+        <v>62.4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -649,14 +649,14 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>39.4</v>
+        <v>43.3</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>58.5</v>
+        <v>62.7</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>46.2</v>
+        <v>47.5</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>61.8</v>
+        <v>76.5</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>47.1</v>
+        <v>37</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>59.7</v>
+        <v>73</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>53.2</v>
+        <v>35.1</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,25 +3749,25 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>44.3</v>
+        <v>47.6</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>66.7</v>
+        <v>48.3</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>41.7</v>
+        <v>53.4</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,25 +3993,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>54.7</v>
+        <v>59.3</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>42.7</v>
+        <v>51.9</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>41.9</v>
+        <v>46.7</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>45.2</v>
+        <v>60</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4359,25 +4359,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>42.9</v>
+        <v>49</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>46.7</v>
+        <v>43.4</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4386,21 +4386,21 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>46.2</v>
+        <v>47.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>40</v>
+        <v>44.2</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>68.3</v>
+        <v>81.2</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -5468,14 +5468,14 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>43.9</v>
+        <v>41.7</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>70</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5701,37 +5701,37 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>62.3</v>
+        <v>52.4</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>39.1</v>
+        <v>47.6</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>55.6</v>
+        <v>47.5</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>40.7</v>
+        <v>37.5</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>60</v>
+        <v>60.3</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -6261,14 +6261,14 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>56.8</v>
+        <v>59.6</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>50</v>
+        <v>56.1</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6555,48 +6555,48 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>53.6</v>
+        <v>46.2</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-D</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="L100" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G100" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="H100" s="4" t="n">
-        <v>151</v>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-D</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="L100" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N100" s="3" t="n">
-        <v>51.7</v>
+        <v>47.1</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>70.7</v>
+        <v>66.2</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -6688,14 +6688,14 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>40.2</v>
+        <v>42.6</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6704,21 +6704,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>69</v>
+        <v>58.3</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>37.9</v>
+        <v>45.8</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6799,48 +6799,48 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>55.4</v>
+        <v>46.9</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-U</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L104" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G104" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="H104" s="4" t="n">
-        <v>157</v>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-D</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="L104" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
       <c r="N104" s="3" t="n">
-        <v>39.2</v>
+        <v>46.2</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7117,14 +7117,14 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>53.1</v>
+        <v>47.7</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>61.5</v>
+        <v>77.3</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>53.3</v>
+        <v>63.2</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8324,14 +8324,14 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>53.3</v>
+        <v>42.1</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8340,10 +8340,10 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -10710,19 +10710,19 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>66.7</v>
+        <v>51.2</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -10730,26 +10730,26 @@
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>54.2</v>
+        <v>56.1</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>100</v>
+        <v>47.1</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -10757,10 +10757,10 @@
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>100</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -11003,48 +11003,48 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>52.9</v>
+        <v>66.7</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="I58" s="3" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-D</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="N58" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="P58" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -11420,57 +11420,57 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>48.8</v>
+        <v>41.7</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>53.5</v>
+        <v>54.2</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>47.1</v>
+        <v>58.3</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>52.9</v>
+        <v>58.3</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12707,25 +12707,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>42.9</v>
+        <v>47.1</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -12734,21 +12734,21 @@
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12991,48 +12991,48 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -13668,10 +13668,10 @@
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>66.7</v>
+        <v>53.8</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -13985,48 +13985,48 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="J100" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-D</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G100" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="N100" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I100" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="J100" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-D</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="N100" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P100" s="3" t="n">
-        <v>54.5</v>
+        <v>58.3</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14127,10 +14127,10 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -14138,14 +14138,14 @@
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>62.5</v>
+        <v>42.9</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14154,21 +14154,21 @@
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>44.4</v>
+        <v>57.1</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -14260,7 +14260,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -14269,25 +14269,25 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>60.7</v>
+        <v>52.4</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I104" s="3" t="n">
-        <v>53.6</v>
+        <v>38.1</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -14296,21 +14296,21 @@
         </is>
       </c>
       <c r="M104" s="3" t="n">
-        <v>52.6</v>
+        <v>63.6</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
-        <v>47.4</v>
+        <v>45.5</v>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>76.5</v>
+        <v>61.8</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>37</v>
+        <v>47.1</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>73</v>
+        <v>59.7</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>35.1</v>
+        <v>53.2</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3322,48 +3322,48 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>56.1</v>
+        <v>54.5</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-U</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H47" s="4" t="n">
-        <v>155</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-D</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="n">
-        <v>35.7</v>
-      </c>
       <c r="O47" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,25 +3993,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>59.3</v>
+        <v>54.7</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>51.9</v>
+        <v>42.7</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>46.7</v>
+        <v>41.9</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>60</v>
+        <v>45.2</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4359,48 +4359,48 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>49</v>
+        <v>42.9</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="G64" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>198</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="L64" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N64" s="3" t="n">
-        <v>44.2</v>
+        <v>40</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5701,37 +5701,37 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>52.4</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>47.6</v>
+        <v>44.7</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>47.5</v>
+        <v>66.7</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>37.5</v>
+        <v>44.4</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>63.2</v>
+        <v>53.3</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8324,14 +8324,14 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>42.1</v>
+        <v>53.3</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8340,10 +8340,10 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10226,10 +10226,10 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>44.1</v>
+        <v>53.8</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -10237,37 +10237,37 @@
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -11003,48 +11003,48 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>66.7</v>
+        <v>52.9</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>60</v>
+        <v>35.3</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
@@ -11420,57 +11420,57 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>41.7</v>
+        <v>48.8</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>54.2</v>
+        <v>53.5</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>58.3</v>
+        <v>47.1</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>58.3</v>
+        <v>52.9</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>57.1</v>
+        <v>90</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -13005,11 +13005,11 @@
         <v>50</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -13018,10 +13018,10 @@
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>59.4</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2235,14 +2235,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>40.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2251,21 +2251,21 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>57.1</v>
+        <v>80</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,25 +3993,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>54.7</v>
+        <v>70</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>42.7</v>
+        <v>50</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>41.9</v>
+        <v>69.2</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>45.2</v>
+        <v>61.5</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5701,37 +5701,37 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>44.7</v>
+        <v>47.6</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>66.7</v>
+        <v>47.5</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>44.4</v>
+        <v>37.5</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8955,22 +8955,22 @@
         <v>100</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -8986,11 +8986,11 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q29" s="4" t="n">
         <v>2</v>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -11003,37 +11003,37 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>35.3</v>
+        <v>60</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>36.4</v>
+        <v>100</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -11041,10 +11041,10 @@
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>45.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>90</v>
+        <v>57.1</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -13005,11 +13005,11 @@
         <v>50</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -13018,10 +13018,10 @@
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>62.4</v>
+        <v>53.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>43.3</v>
+        <v>41.6</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,21 +665,21 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>62.7</v>
+        <v>51.5</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>47.5</v>
+        <v>42.6</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,25 +1004,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>60.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>38.7</v>
+        <v>38</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>69.7</v>
+        <v>68</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>42.4</v>
+        <v>40</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>48.5</v>
+        <v>56.9</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1381,14 +1381,14 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>46.2</v>
+        <v>44.6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1397,21 +1397,21 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>50</v>
+        <v>52.2</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>48.8</v>
+        <v>45.6</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>45.1</v>
+        <v>58.2</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1442,26 +1442,26 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>44.5</v>
+        <v>41.2</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>45.6</v>
+        <v>49.2</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>48.5</v>
+        <v>42.9</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1614,25 +1614,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>58.8</v>
+        <v>55</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1641,21 +1641,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>80</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>80</v>
+        <v>46.2</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1980,25 +1980,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>55.7</v>
+        <v>73</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>42.3</v>
+        <v>38.2</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>50.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>45.9</v>
+        <v>44.2</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,48 +2041,48 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>44.9</v>
+        <v>47.5</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>158</v>
+        <v>61</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>41.1</v>
+        <v>36.1</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>158</v>
+        <v>61</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>44.1</v>
+        <v>45</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,48 +2224,48 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>85.7</v>
+        <v>60</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K29" s="3" t="n">
         <v>100</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>49.1</v>
+        <v>63.7</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2418,37 +2418,37 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>50</v>
+        <v>40.2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>46.3</v>
+        <v>63.9</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>51.2</v>
+        <v>36.1</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2651,25 +2651,25 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>48.6</v>
+        <v>64.2</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>48.6</v>
+        <v>41.8</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>47.5</v>
+        <v>58.6</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2723,14 +2723,14 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>46.2</v>
+        <v>36.8</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>52.2</v>
+        <v>40</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>58.2</v>
+        <v>53.3</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,48 +3017,48 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>51.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>37</v>
+        <v>46.2</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>58.3</v>
+        <v>57.1</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>61.5</v>
+        <v>63.8</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3089,14 +3089,14 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>46.2</v>
+        <v>47.8</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>72.7</v>
+        <v>58.6</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>48.5</v>
+        <v>62.1</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>57.4</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3394,37 +3394,37 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>44.3</v>
+        <v>40.6</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>50</v>
+        <v>60.5</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>50</v>
+        <v>42.1</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,25 +3749,25 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>44.8</v>
+        <v>60.9</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>143</v>
+        <v>46</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>143</v>
+        <v>46</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>48.3</v>
+        <v>56.2</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>53.4</v>
+        <v>56.2</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>68.8</v>
+        <v>48</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -4004,37 +4004,37 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>43.8</v>
+        <v>52</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>85.7</v>
+        <v>37.5</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4298,25 +4298,25 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>73.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>55.6</v>
+        <v>55.1</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4325,21 +4325,21 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>66.7</v>
+        <v>73</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>52.4</v>
+        <v>56.8</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>65.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4431,14 +4431,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>44.2</v>
+        <v>47.1</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>45.3</v>
+        <v>44</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>61.9</v>
+        <v>50</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -4553,14 +4553,14 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4725,25 +4725,25 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>65.5</v>
+        <v>57.7</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>40.8</v>
+        <v>42.3</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>71.2</v>
+        <v>63.6</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>40.7</v>
+        <v>50</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5030,37 +5030,37 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-D</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="E75" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="H75" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="n">
-        <v>63.6</v>
-      </c>
       <c r="L75" s="4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>45.5</v>
+        <v>55.6</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>56.6</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5163,14 +5163,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>45</v>
+        <v>37.8</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>60.8</v>
+        <v>69.2</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>51</v>
+        <v>42.3</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5396,25 +5396,25 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>58.1</v>
+        <v>51.7</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>42.7</v>
+        <v>41.7</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>59.6</v>
+        <v>50</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>42.3</v>
+        <v>38.5</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>81.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -5468,14 +5468,14 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>41.7</v>
+        <v>43.6</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>54.3</v>
+        <v>55.7</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>173</v>
+        <v>61</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5956,14 +5956,14 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>42.2</v>
+        <v>42.6</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>173</v>
+        <v>61</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>53.3</v>
+        <v>54.5</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>42.7</v>
+        <v>54.5</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6128,48 +6128,48 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>47.3</v>
+        <v>52.9</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>51.4</v>
+        <v>44.4</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>54.3</v>
+        <v>50</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="94">
@@ -6250,37 +6250,37 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="n">
         <v>60.3</v>
       </c>
-      <c r="E95" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H95" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-D</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="n">
-        <v>59.6</v>
-      </c>
       <c r="L95" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>56.1</v>
+        <v>56.9</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="96">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6311,25 +6311,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>48.5</v>
+        <v>56</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>39.4</v>
+        <v>50</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6338,21 +6338,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>58.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>37.9</v>
+        <v>52.6</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>52.1</v>
+        <v>61.9</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6505,14 +6505,14 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>43.1</v>
+        <v>39.3</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>54.1</v>
+        <v>59.4</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>42.6</v>
+        <v>40.6</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6555,25 +6555,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>46.2</v>
+        <v>60.8</v>
       </c>
       <c r="E100" s="4" t="n">
         <v>143</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>47.6</v>
+        <v>46.9</v>
       </c>
       <c r="H100" s="4" t="n">
         <v>143</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>41.4</v>
+        <v>58.8</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6677,25 +6677,25 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>66.2</v>
+        <v>74.3</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6704,21 +6704,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>58.3</v>
+        <v>77.3</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>45.8</v>
+        <v>54.5</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>52.6</v>
+        <v>52.3</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7117,14 +7117,14 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>57.9</v>
+        <v>45.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>55.6</v>
+        <v>56.5</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>44.4</v>
+        <v>39.1</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7532,25 +7532,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>58.6</v>
+        <v>64.7</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>44.8</v>
+        <v>41.2</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7559,21 +7559,21 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>77.8</v>
+        <v>66.7</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -7958,25 +7958,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>53.8</v>
+        <v>65.3</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>46.2</v>
+        <v>49</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -7985,21 +7985,21 @@
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>38.5</v>
+        <v>55.6</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8029,25 +8029,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>44.2</v>
+        <v>57.1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>46.5</v>
+        <v>42.9</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8056,21 +8056,21 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>61.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8242,48 +8242,48 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8668,25 +8668,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>53.7</v>
+        <v>80</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>41.5</v>
+        <v>55</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -8695,21 +8695,21 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>52.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>58.8</v>
+        <v>57.1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -8730,19 +8730,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>48.7</v>
+        <v>46.7</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -8750,26 +8750,26 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -8943,39 +8943,39 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M29" s="3" t="n">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9165,10 +9165,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -9176,14 +9176,14 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9192,21 +9192,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>58.3</v>
+        <v>57.1</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>41.7</v>
+        <v>42.9</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9449,48 +9449,48 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>42.1</v>
+        <v>55.6</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>52.6</v>
+        <v>66.7</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9520,48 +9520,48 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>55</v>
+        <v>58.8</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>47.5</v>
+        <v>35.3</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9875,48 +9875,48 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9946,25 +9946,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>57.1</v>
+        <v>63.6</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -9973,10 +9973,10 @@
         </is>
       </c>
       <c r="M43" s="3" t="n">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -9984,10 +9984,10 @@
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>54.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10301,10 +10301,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>66.7</v>
+        <v>72.2</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -10315,23 +10315,23 @@
         <v>41.7</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -10339,10 +10339,10 @@
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10727,25 +10727,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>44</v>
+        <v>85.7</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="M54" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="N54" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="Q54" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -11002,19 +11002,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -11025,11 +11025,11 @@
         <v>50</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -11366,25 +11366,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>41.7</v>
+        <v>69.2</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -11400,11 +11400,11 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
-        <v>33.3</v>
+        <v>83.3</v>
       </c>
       <c r="Q63" s="4" t="n">
         <v>6</v>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11508,25 +11508,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>51.4</v>
+        <v>45</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -11535,21 +11535,21 @@
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>58.8</v>
+        <v>70</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -11650,48 +11650,44 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I67" s="3" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr"/>
       <c r="N67" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr"/>
       <c r="Q67" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -11854,7 +11850,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11863,25 +11859,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>70</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>45</v>
+        <v>47.1</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -11893,18 +11889,18 @@
         <v>75</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P70" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -12209,7 +12205,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -12218,25 +12214,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>75</v>
+        <v>77.8</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I75" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -12252,11 +12248,11 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P75" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q75" s="4" t="n">
         <v>3</v>
@@ -12351,7 +12347,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12360,25 +12356,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>59.4</v>
+        <v>85.2</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>43.8</v>
+        <v>40.7</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12387,21 +12383,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>64.3</v>
+        <v>42.9</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -12635,7 +12631,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12644,25 +12640,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>42.9</v>
+        <v>41.7</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -12671,10 +12667,10 @@
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>68.8</v>
+        <v>57.1</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -12682,10 +12678,10 @@
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -12706,7 +12702,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12715,25 +12711,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>37.5</v>
+        <v>55.6</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -12745,18 +12741,18 @@
         <v>100</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -13274,7 +13270,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -13283,10 +13279,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>68.5</v>
+        <v>57.1</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -13294,14 +13290,14 @@
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>46.3</v>
+        <v>57.1</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -13310,21 +13306,21 @@
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>56.5</v>
+        <v>100</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>47.8</v>
+        <v>100</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -13487,7 +13483,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -13496,10 +13492,10 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>61.9</v>
+        <v>53.7</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -13507,30 +13503,30 @@
         </is>
       </c>
       <c r="I93" s="3" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="J93" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-D</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="J93" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-U</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M93" s="3" t="n">
-        <v>60</v>
       </c>
       <c r="N93" s="4" t="n">
         <v>10</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
@@ -13700,7 +13696,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13709,48 +13705,48 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>54.5</v>
+        <v>57.1</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>39.4</v>
+        <v>57.1</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -13913,7 +13909,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13922,10 +13918,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -13933,14 +13929,14 @@
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -13949,21 +13945,21 @@
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>43.8</v>
+        <v>36.4</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100">
@@ -13984,7 +13980,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -13993,25 +13989,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>51.7</v>
+        <v>61.3</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>48.3</v>
+        <v>51.6</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14023,7 +14019,7 @@
         <v>66.7</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -14031,10 +14027,10 @@
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
@@ -14126,7 +14122,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14135,48 +14131,48 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,25 +1004,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>38</v>
+        <v>38.7</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>68</v>
+        <v>69.7</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>40</v>
+        <v>42.4</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>56.9</v>
+        <v>48.5</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1381,14 +1381,14 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>44.6</v>
+        <v>46.2</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1397,21 +1397,21 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>45.6</v>
+        <v>48.8</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>58.2</v>
+        <v>45.1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1442,26 +1442,26 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>41.2</v>
+        <v>44.5</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>49.2</v>
+        <v>45.6</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>42.9</v>
+        <v>48.5</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1980,25 +1980,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>73</v>
+        <v>55.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>38.2</v>
+        <v>42.3</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>44.2</v>
+        <v>45.9</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,48 +2041,48 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>47.5</v>
+        <v>44.9</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>36.1</v>
+        <v>41.1</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>45</v>
+        <v>44.1</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>45</v>
+        <v>45.8</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2346,25 +2346,25 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>68.8</v>
+        <v>81.5</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>39.6</v>
+        <v>61.1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>68</v>
+        <v>77.3</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>48</v>
+        <v>59.1</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>63.7</v>
+        <v>49.1</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2418,37 +2418,37 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>40.2</v>
+        <v>50</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>63.9</v>
+        <v>46.3</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>36.1</v>
+        <v>51.2</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>58.6</v>
+        <v>47.5</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2723,14 +2723,14 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>36.8</v>
+        <v>46.2</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>40</v>
+        <v>52.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>53.3</v>
+        <v>58.2</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,48 +3017,48 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>46.2</v>
+        <v>42.9</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>57.1</v>
+        <v>87.5</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3261,25 +3261,25 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>50.9</v>
+        <v>53.2</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>45.3</v>
+        <v>43.6</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3288,21 +3288,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>41.7</v>
+        <v>47.2</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>48.6</v>
+        <v>43.4</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,25 +3383,25 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>60.5</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>40.6</v>
+        <v>48.3</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>60.5</v>
+        <v>78.8</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>42.1</v>
+        <v>51.5</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4431,14 +4431,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>47.1</v>
+        <v>44.2</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4447,21 +4447,21 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="L65" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="L65" s="4" t="n">
-        <v>25</v>
-      </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>44</v>
+        <v>45.3</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4725,25 +4725,25 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>57.7</v>
+        <v>65.5</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>42.3</v>
+        <v>40.8</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>63.6</v>
+        <v>71.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>50</v>
+        <v>40.7</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>56.6</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5163,14 +5163,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>37.8</v>
+        <v>45</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>69.2</v>
+        <v>60.8</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>42.3</v>
+        <v>51</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5396,25 +5396,25 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>51.7</v>
+        <v>58.1</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>41.7</v>
+        <v>42.7</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>50</v>
+        <v>59.6</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>38.5</v>
+        <v>42.3</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>55.7</v>
+        <v>54.3</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>61</v>
+        <v>173</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5956,14 +5956,14 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>61</v>
+        <v>173</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>54.5</v>
+        <v>53.3</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>54.5</v>
+        <v>42.7</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>22</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6311,25 +6311,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>56</v>
+        <v>48.5</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>50</v>
+        <v>39.4</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6338,21 +6338,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>52.6</v>
+        <v>37.9</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>61.9</v>
+        <v>52.1</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6505,14 +6505,14 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>39.3</v>
+        <v>43.1</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>59.4</v>
+        <v>54.1</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>40.6</v>
+        <v>42.6</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7532,25 +7532,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>64.7</v>
+        <v>58.6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>41.2</v>
+        <v>44.8</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7559,21 +7559,21 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -7958,25 +7958,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>65.3</v>
+        <v>53.8</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>49</v>
+        <v>46.2</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -7985,21 +7985,21 @@
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>55.6</v>
+        <v>38.5</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8029,25 +8029,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>57.1</v>
+        <v>44.2</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>42.9</v>
+        <v>46.5</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8056,21 +8056,21 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>66.7</v>
+        <v>61.5</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8668,25 +8668,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>80</v>
+        <v>53.7</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>55</v>
+        <v>41.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -8695,21 +8695,21 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -8730,57 +8730,57 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>46.7</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="Q26" s="4" t="n">
         <v>15</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>87.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -9105,14 +9105,14 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>75</v>
+        <v>61.5</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>5</v>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="Q31" s="4" t="n">
         <v>5</v>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9165,10 +9165,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -9176,14 +9176,14 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9192,21 +9192,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>57.1</v>
+        <v>58.3</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>42.9</v>
+        <v>41.7</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9520,48 +9520,48 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>58.8</v>
+        <v>55</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>35.3</v>
+        <v>47.5</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -9866,57 +9866,57 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10159,25 +10159,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>48.5</v>
+        <v>58.7</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>36.4</v>
+        <v>47.8</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -10186,10 +10186,10 @@
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>43.8</v>
+        <v>53.8</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>37.5</v>
+        <v>46.2</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10301,25 +10301,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>72.2</v>
+        <v>62</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10328,21 +10328,21 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>57.1</v>
+        <v>54.5</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11508,25 +11508,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>70</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>45</v>
+        <v>51.4</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -11535,21 +11535,21 @@
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>70</v>
+        <v>58.8</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11859,25 +11859,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>47.1</v>
+        <v>45</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -11889,18 +11889,18 @@
         <v>75</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P70" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12356,25 +12356,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>85.2</v>
+        <v>59.4</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>40.7</v>
+        <v>43.8</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12383,21 +12383,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>42.9</v>
+        <v>64.3</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12640,25 +12640,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>41.7</v>
+        <v>42.9</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>57.1</v>
+        <v>68.8</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -13279,10 +13279,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>57.1</v>
+        <v>68.5</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -13290,14 +13290,14 @@
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>57.1</v>
+        <v>46.3</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -13306,21 +13306,21 @@
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>100</v>
+        <v>56.5</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>100</v>
+        <v>47.8</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13705,48 +13705,48 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>57.1</v>
+        <v>54.5</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>57.1</v>
+        <v>39.4</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13918,10 +13918,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>84.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -13929,14 +13929,14 @@
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -13945,21 +13945,21 @@
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>72.7</v>
+        <v>75</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>36.4</v>
+        <v>43.8</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -6302,7 +6302,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6311,25 +6311,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>48.5</v>
+        <v>54.2</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>39.4</v>
+        <v>44.4</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6338,21 +6338,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>58.6</v>
+        <v>60</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>37.9</v>
+        <v>45</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6677,25 +6677,25 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>74.3</v>
+        <v>71.3</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>42.9</v>
+        <v>39.4</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>77.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>54.5</v>
+        <v>44.8</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103">
@@ -13696,57 +13696,53 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>39.4</v>
+        <v>50</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M96" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P96" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="inlineStr"/>
       <c r="Q96" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -14122,7 +14118,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14131,48 +14127,48 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="G102" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="n">
+      <c r="N102" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J102" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N102" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="n">
-        <v>60</v>
-      </c>
       <c r="Q102" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>60.5</v>
+        <v>55.7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>47.4</v>
+        <v>41.8</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>65.2</v>
+        <v>55.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>50.7</v>
+        <v>48.1</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>69</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>70.7</v>
+        <v>62.3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -832,14 +832,14 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>46.3</v>
+        <v>44</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>44.7</v>
+        <v>47.8</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>43</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>57.6</v>
+        <v>69.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1015,14 +1015,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>44.7</v>
+        <v>39.6</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>52.8</v>
+        <v>80.8</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>47.2</v>
+        <v>46.2</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>49</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1381,14 +1381,14 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>39.7</v>
+        <v>45</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>77.8</v>
+        <v>46.6</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>44.4</v>
+        <v>55.2</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>72</v>
+        <v>67.8</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2418,14 +2418,14 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>40</v>
+        <v>44.8</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>72.7</v>
+        <v>61.4</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>40.9</v>
+        <v>45.6</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>62.3</v>
+        <v>63.8</v>
       </c>
       <c r="E36" s="4" t="n">
         <v>69</v>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>47.8</v>
+        <v>52.2</v>
       </c>
       <c r="L36" s="4" t="n">
         <v>23</v>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,48 +3017,48 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>48.1</v>
+        <v>66.7</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-N</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n">
         <v>44.4</v>
       </c>
-      <c r="H42" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-U</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>40</v>
-      </c>
       <c r="O42" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>57.7</v>
+        <v>65</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -3272,14 +3272,14 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>41.7</v>
+        <v>42.5</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3288,21 +3288,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>56.9</v>
+        <v>59.4</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>44.6</v>
+        <v>43.8</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>66.7</v>
+        <v>63.5</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3760,26 +3760,26 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>52.2</v>
+        <v>47.6</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4237,25 +4237,25 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>77.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4264,21 +4264,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
         <v>57.1</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4481,25 +4481,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>68.8</v>
+        <v>63</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>36.2</v>
+        <v>47.2</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4508,21 +4508,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>39.3</v>
+        <v>46.8</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K67" s="3" t="n">
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>53.9</v>
+        <v>54.5</v>
       </c>
       <c r="E78" s="4" t="n">
         <v>191</v>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>57.5</v>
+        <v>58.8</v>
       </c>
       <c r="L78" s="4" t="n">
         <v>80</v>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>62.6</v>
+        <v>53.7</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5407,14 +5407,14 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>40.5</v>
+        <v>41.8</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5423,21 +5423,21 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>63.5</v>
+        <v>54.5</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>38.5</v>
+        <v>45.5</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5457,25 +5457,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>44.7</v>
+        <v>45.2</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>45.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>36.4</v>
+        <v>58.8</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>69.3</v>
+        <v>58.1</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5773,14 +5773,14 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>36.4</v>
+        <v>45.9</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5789,21 +5789,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>42.3</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>44.8</v>
+        <v>44.2</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>61</v>
+        <v>60.5</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>50.8</v>
+        <v>51.3</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>57.6</v>
+        <v>58.3</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6311,25 +6311,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>64.7</v>
+        <v>50</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
         <v>45.1</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6338,21 +6338,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>54.2</v>
+        <v>45.9</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>54.2</v>
+        <v>56.8</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6372,25 +6372,25 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>44.1</v>
+        <v>37.8</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6399,21 +6399,21 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>67.2</v>
+        <v>61.5</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>44.8</v>
+        <v>50</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6555,25 +6555,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>60.4</v>
+        <v>60.6</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>39</v>
+        <v>39.4</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>55.2</v>
+        <v>61.3</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>43.3</v>
+        <v>38.7</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6677,25 +6677,25 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>71.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>42.4</v>
+        <v>39</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="L102" s="4" t="n">
         <v>36</v>
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>47.2</v>
+        <v>36.1</v>
       </c>
       <c r="O102" s="4" t="n">
         <v>36</v>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7106,48 +7106,48 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>46.7</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>56.2</v>
+        <v>46.7</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>69.2</v>
+        <v>50</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7319,10 +7319,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>80</v>
+        <v>48.3</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7330,14 +7330,14 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>60</v>
+        <v>44.8</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>77.8</v>
+        <v>43.8</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>55.6</v>
+        <v>43.8</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7532,25 +7532,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7559,21 +7559,21 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>64.3</v>
+        <v>61.5</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -7969,26 +7969,26 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>42.9</v>
+        <v>57.7</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>84.2</v>
+        <v>70</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -9172,14 +9172,14 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>42.1</v>
+        <v>40</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9188,21 +9188,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>80</v>
+        <v>77.8</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>40</v>
+        <v>44.4</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9871,25 +9871,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -9898,21 +9898,21 @@
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>58.1</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -10166,14 +10166,14 @@
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>48.4</v>
+        <v>52.6</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10723,30 +10723,30 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>72.7</v>
+        <v>77.8</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>45.5</v>
+        <v>55.6</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M54" s="3" t="n">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P54" s="3" t="n">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11291,48 +11291,48 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>83.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G62" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>D-U-N-U</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N62" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>D-U-N-N</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N62" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P62" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11575,10 +11575,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -11586,14 +11586,14 @@
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>47.1</v>
+        <v>58.6</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11602,21 +11602,21 @@
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>85.7</v>
+        <v>50</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>42.9</v>
+        <v>55.6</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12640,48 +12640,48 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>37</v>
+        <v>41.7</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
@@ -12702,57 +12702,57 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13066,25 +13066,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>57.9</v>
+        <v>63.6</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>42.1</v>
+        <v>54.5</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -13093,21 +13093,21 @@
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>60</v>
+        <v>72.7</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>60</v>
+        <v>36.4</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13705,48 +13705,48 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>54.5</v>
       </c>
       <c r="G96" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>D-N-U-U</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="N96" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="n">
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="n">
         <v>57.1</v>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="Q96" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-N</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M96" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N96" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P96" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q96" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13776,25 +13776,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>71</v>
+        <v>84.2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>48.4</v>
+        <v>36.8</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -13803,21 +13803,21 @@
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>69.2</v>
+        <v>60</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>53.8</v>
+        <v>60</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -13989,25 +13989,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>53.8</v>
+        <v>64.7</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>50</v>
+        <v>41.2</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14016,10 +14016,10 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>57.1</v>
+        <v>62.5</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -14027,10 +14027,10 @@
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>57.1</v>
+        <v>43.8</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14131,48 +14131,48 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="G102" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-D</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="N102" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="n">
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="n">
         <v>45.5</v>
       </c>
-      <c r="J102" s="4" t="n">
+      <c r="Q102" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-D</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="N102" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q102" s="4" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="103">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>55.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>41.8</v>
+        <v>38.3</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,21 +665,21 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>48.1</v>
+        <v>37.5</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,25 +1309,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>68.8</v>
+        <v>69.7</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>43.8</v>
+        <v>35.5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,21 +1336,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,25 +2895,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>59</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>40.5</v>
+        <v>48.7</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>75</v>
+        <v>54.1</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>37.5</v>
+        <v>51.4</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3200,25 +3200,25 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>51.9</v>
+        <v>63.2</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>187</v>
+        <v>68</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>44.4</v>
+        <v>42.6</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>187</v>
+        <v>68</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3261,25 +3261,25 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>60.6</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>42.2</v>
+        <v>37.9</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3288,21 +3288,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>55</v>
+        <v>58.8</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>40</v>
+        <v>44.1</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3322,25 +3322,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>64.8</v>
+        <v>56.2</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>49.3</v>
+        <v>41.8</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3349,21 +3349,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>63.2</v>
+        <v>54.4</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>42.1</v>
+        <v>43.9</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,48 +3749,48 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>63.5</v>
+        <v>45.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-D</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H54" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-D</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>52.4</v>
-      </c>
       <c r="L54" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>47.6</v>
+        <v>42.3</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4237,25 +4237,25 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>46.6</v>
+        <v>52.4</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4264,21 +4264,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>63.2</v>
+        <v>52.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4675,14 +4675,14 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>63.2</v>
+        <v>59.3</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>61.5</v>
+        <v>54.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>61.5</v>
+        <v>59.1</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5213,25 +5213,25 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>54.1</v>
+        <v>54.7</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>43.2</v>
+        <v>42.7</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>57.6</v>
+        <v>59.3</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>48.5</v>
+        <v>45.7</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5457,25 +5457,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>69</v>
+        <v>76.5</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>45.2</v>
+        <v>41.2</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5579,10 +5579,10 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>59.7</v>
+        <v>61.4</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>46.1</v>
+        <v>42.9</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5606,21 +5606,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>64.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>47.1</v>
+        <v>46.4</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6250,25 +6250,25 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>60.5</v>
+        <v>62.4</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>51.3</v>
+        <v>40</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>60</v>
+        <v>56.1</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>58.3</v>
+        <v>43.9</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="96">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6555,25 +6555,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>60.6</v>
+        <v>75</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>39.4</v>
+        <v>45.5</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6582,21 +6582,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>61.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>38.7</v>
+        <v>55.9</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -6688,14 +6688,14 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>39</v>
+        <v>43.5</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>77.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>36.1</v>
+        <v>48.1</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>52</v>
+        <v>60.8</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -6749,14 +6749,14 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>44.1</v>
+        <v>41.8</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6765,21 +6765,21 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>57.9</v>
+        <v>51.9</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>49.1</v>
+        <v>48.1</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7106,25 +7106,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>50</v>
+        <v>81.8</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>42.9</v>
+        <v>45.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7136,18 +7136,18 @@
         <v>66.7</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7887,48 +7887,48 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>U-N-U-D</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>U-N-U-N</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="N14" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9733,25 +9733,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>45.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -9760,21 +9760,21 @@
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10088,48 +10088,48 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>46.2</v>
+        <v>61.5</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>51.3</v>
+        <v>38.5</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10159,25 +10159,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>45.5</v>
+        <v>64.3</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -10186,21 +10186,21 @@
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10230,25 +10230,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>58.8</v>
+        <v>63.9</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>35.3</v>
+        <v>33.3</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -10257,10 +10257,10 @@
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>55.6</v>
+        <v>56.2</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -10268,10 +10268,10 @@
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>44.4</v>
+        <v>43.8</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
@@ -10718,19 +10718,19 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>44.4</v>
+        <v>56.7</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -10738,37 +10738,37 @@
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>55.6</v>
+        <v>63.3</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11295,10 +11295,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -11309,34 +11309,34 @@
         <v>50</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P62" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -11783,57 +11783,57 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I69" s="3" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M69" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P69" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12431,10 +12431,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>77.8</v>
+        <v>62.5</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -12442,14 +12442,14 @@
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>55.6</v>
+        <v>45</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -12458,10 +12458,10 @@
         </is>
       </c>
       <c r="M78" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -12469,10 +12469,10 @@
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
@@ -12706,57 +12706,53 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P82" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr"/>
       <c r="Q82" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -12848,7 +12844,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12857,10 +12853,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>59.5</v>
+        <v>68.8</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -12868,14 +12864,14 @@
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -12884,10 +12880,10 @@
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -12895,10 +12891,10 @@
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -13629,7 +13625,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13638,48 +13634,48 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>58.6</v>
+        <v>54.5</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>48.3</v>
+        <v>45.5</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
@@ -13984,7 +13980,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -13993,10 +13989,10 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>77.8</v>
+        <v>87.5</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -14004,14 +14000,14 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14020,10 +14016,10 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -14031,10 +14027,10 @@
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -14126,7 +14122,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14135,37 +14131,37 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>50</v>
+        <v>38.5</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>83.3</v>
+        <v>60</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -14173,10 +14169,10 @@
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -14197,7 +14193,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -14206,25 +14202,25 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>40.7</v>
+        <v>35</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -14233,21 +14229,21 @@
         </is>
       </c>
       <c r="M103" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N103" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">

--- a/BIS_tr.xlsx
+++ b/BIS_tr.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -649,14 +649,14 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>47.6</v>
+        <v>43.4</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,21 +665,21 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>53.3</v>
+        <v>61.5</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>53.3</v>
+        <v>46.2</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,25 +1248,25 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>55.6</v>
+        <v>47.8</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44.4</v>
+        <v>39.1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,25 +2041,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>62.9</v>
+        <v>56.6</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>40.3</v>
+        <v>38.6</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,25 +3017,25 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>54.5</v>
+        <v>44.8</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>45.5</v>
+        <v>48.3</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>51.8</v>
+        <v>47.9</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3760,37 +3760,37 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>45.3</v>
+        <v>49.6</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>48.5</v>
+        <v>43.5</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>48.5</v>
+        <v>54.8</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4359,25 +4359,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>60.3</v>
+        <v>46.2</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>58</v>
+        <v>184</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>41.4</v>
+        <v>45.7</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>58</v>
+        <v>184</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>59.1</v>
+        <v>47.1</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>40.9</v>
+        <v>44.3</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>87</v>
+        <v>87.5</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -5468,14 +5468,14 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>43.5</v>
+        <v>45.8</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5762,25 +5762,25 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>52.9</v>
+        <v>71.2</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>155</v>
+        <v>66</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>41.9</v>
+        <v>45.5</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>155</v>
+        <v>66</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5789,21 +5789,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>61.3</v>
+        <v>66.7</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>48.4</v>
+        <v>55.6</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6250,25 +6250,25 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>63</v>
+        <v>75.7</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>44.6</v>
+        <v>41.7</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>52.9</v>
+        <v>77.5</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>52.9</v>
+        <v>40</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6555,25 +6555,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>72</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>46</v>
+        <v>38.9</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6582,21 +6582,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>69.2</v>
+        <v>81.2</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>61.5</v>
+        <v>43.8</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6677,25 +6677,25 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>38.9</v>
+        <v>43</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6704,21 +6704,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>70</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>46.7</v>
+        <v>45.9</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="103">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>77.8</v>
+        <v>62.5</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7117,14 +7117,14 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>55.6</v>
+        <v>43.8</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7133,21 +7133,21 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -7803,57 +7803,57 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8731,37 +8731,37 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>73.3</v>
+        <v>55</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>53.3</v>
+        <v>40</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -8769,10 +8769,10 @@
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9870,41 +9870,45 @@
         <v>100</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J42" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>N-U-U-D</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N42" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>N-U-U-N</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr"/>
-      <c r="N42" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -10706,7 +10710,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10715,37 +10719,37 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>57.8</v>
+        <v>53.8</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>48.9</v>
+        <v>61.5</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -10753,10 +10757,10 @@
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>45.5</v>
+        <v>57.1</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -11416,7 +11420,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11425,37 +11429,37 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-D</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="G64" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="J64" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-N</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="N64" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -11466,7 +11470,7 @@
         <v>50</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
@@ -12694,7 +12698,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12703,25 +12707,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>4</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -13049,7 +13053,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13058,25 +13062,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>56.2</v>
+        <v>77.8</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -13085,21 +13089,21 @@
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>53.8</v>
+        <v>66.7</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>46.2</v>
+        <v>44.4</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
@@ -13617,7 +13621,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13626,25 +13630,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>41.2</v>
+        <v>57.1</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13653,10 +13657,10 @@
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>57.1</v>
+        <v>87.5</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -13664,10 +13668,10 @@
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -13972,7 +13976,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -13981,25 +13985,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>36.4</v>
+        <v>57.1</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14008,21 +14012,21 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -14114,7 +14118,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14123,25 +14127,25 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>77.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
         <v>44.4</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14150,21 +14154,21 @@
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
